--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486459_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486459_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0585</v>
+        <v>2.975</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1386</v>
+        <v>2.2504</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.7247</v>
       </c>
       <c r="G2" t="n">
         <v>0.7314000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5446</v>
+        <v>0.4612</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2139</v>
+        <v>-0.1021</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7585</v>
+        <v>0.5633</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1384</v>
+        <v>1.6895</v>
       </c>
       <c r="E3" t="n">
-        <v>2.011</v>
+        <v>2.3463</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8726</v>
+        <v>-0.6569</v>
       </c>
       <c r="G3" t="n">
         <v>0.8633999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.2247</v>
+        <v>-1.6737</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0274</v>
+        <v>-0.6922</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1973</v>
+        <v>-0.9815</v>
       </c>
       <c r="V3" t="n">
         <v>2.0647</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.796</v>
+        <v>0.6273</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7214</v>
+        <v>-0.6463</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0746</v>
+        <v>1.2737</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.4151</v>
+        <v>0.2188</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9098</v>
+        <v>1.3806</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5052</v>
+        <v>-1.1618</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6657999999999999</v>
+        <v>0.1576</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3925</v>
+        <v>1.5329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7267</v>
+        <v>-1.3754</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7493</v>
+        <v>0.0612</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5173</v>
+        <v>-0.1523</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.232</v>
+        <v>0.2136</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5415</v>
+        <v>0.5215</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3447</v>
+        <v>0.2836</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1968</v>
+        <v>0.2379</v>
       </c>
       <c r="V4" t="n">
-        <v>1.017</v>
+        <v>-0.113</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.113</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4721</v>
+        <v>0.5377</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3044</v>
+        <v>2.6571</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8323</v>
+        <v>-2.1195</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2016</v>
+        <v>0.9748</v>
       </c>
       <c r="H5" t="n">
-        <v>0.082</v>
+        <v>1.8003</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1196</v>
+        <v>-0.8255</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3389</v>
+        <v>2.6906</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2624</v>
+        <v>2.1352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0765</v>
+        <v>0.5554</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1372</v>
+        <v>-1.7158</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1803</v>
+        <v>-0.3348</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0431</v>
+        <v>-1.381</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.852</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>-0.5984</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8702</v>
+        <v>-0.2536</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4038</v>
+        <v>0.4774</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8699</v>
+        <v>1.52</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2737</v>
+        <v>-1.0426</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2188</v>
+        <v>-0.5638</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3806</v>
+        <v>-0.3924</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1618</v>
+        <v>-0.1713</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1576</v>
+        <v>1.0389</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5329</v>
+        <v>0.0428</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3754</v>
+        <v>0.9961</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0612</v>
+        <v>-1.6027</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1523</v>
+        <v>-0.4353</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136</v>
+        <v>-1.1674</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>0.298</v>
+        <v>-1.4814</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0601</v>
+        <v>-0.6489</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2379</v>
+        <v>-0.8325</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.113</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.113</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3141</v>
+        <v>0.4413</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4336</v>
+        <v>1.3044</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1195</v>
+        <v>-0.8632</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9748</v>
+        <v>1.2016</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8003</v>
+        <v>0.082</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8255</v>
+        <v>1.1196</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6906</v>
+        <v>1.3389</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1352</v>
+        <v>1.2624</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5554</v>
+        <v>0.0765</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7158</v>
+        <v>-0.1372</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3348</v>
+        <v>-1.1803</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.381</v>
+        <v>1.0431</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0755</v>
+        <v>-0.9779</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.0769</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2536</v>
+        <v>-0.901</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8902</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1854</v>
+        <v>-0.6068</v>
       </c>
       <c r="E8" t="n">
-        <v>1.073</v>
+        <v>-0.6197</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2584</v>
+        <v>0.013</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5638</v>
+        <v>-2.4151</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3924</v>
+        <v>-1.9098</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1713</v>
+        <v>-0.5052</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0389</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0428</v>
+        <v>-1.3925</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9961</v>
+        <v>0.7267</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6027</v>
+        <v>-1.7493</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4353</v>
+        <v>-0.5173</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1674</v>
+        <v>-1.232</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1442</v>
+        <v>0.1388</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0959</v>
+        <v>0.0036</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0482</v>
+        <v>0.1352</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.017</v>
       </c>
       <c r="W8" t="n">
         <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4113</v>
+        <v>-0.7255</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4516</v>
+        <v>-3.1326</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8629</v>
+        <v>2.4071</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7443</v>
+        <v>-0.9872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9093</v>
+        <v>1.6512</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.165</v>
+        <v>-2.6383</v>
       </c>
       <c r="J9" t="n">
-        <v>0.272</v>
+        <v>-2.0739</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8641</v>
+        <v>0.6935</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5921</v>
+        <v>-2.7674</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4723</v>
+        <v>1.0868</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0452</v>
+        <v>0.9577</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4271</v>
+        <v>0.1291</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.0451</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5674</v>
+        <v>0.1571</v>
       </c>
       <c r="T9" t="n">
-        <v>2.8348</v>
+        <v>0.0288</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2674</v>
+        <v>0.1283</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.678</v>
+        <v>-0.113</v>
       </c>
       <c r="W9" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3729</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4154</v>
+        <v>-2.3996</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9149</v>
+        <v>-1.4958</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4996</v>
+        <v>-0.9038</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9872</v>
+        <v>-3.4061</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6512</v>
+        <v>-2.6946</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6383</v>
+        <v>-0.7115</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0739</v>
+        <v>-2.2194</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6935</v>
+        <v>-1.9948</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.7674</v>
+        <v>-0.2246</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0868</v>
+        <v>-1.1867</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9577</v>
+        <v>-0.6998</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1291</v>
+        <v>-0.4869</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5327</v>
+        <v>0.1619</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.1586</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2207</v>
+        <v>0.0033</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.113</v>
+        <v>-0.678</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.113</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6713</v>
+        <v>-2.4653</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6134</v>
+        <v>-1.4482</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0579</v>
+        <v>-1.0171</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4061</v>
+        <v>0.7443</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6946</v>
+        <v>0.9093</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7115</v>
+        <v>-0.165</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2194</v>
+        <v>0.272</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9948</v>
+        <v>0.8641</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2246</v>
+        <v>-0.5921</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1867</v>
+        <v>0.4723</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6998</v>
+        <v>0.0452</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4869</v>
+        <v>0.4271</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5225</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1098</v>
+        <v>0.5134</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9589</v>
+        <v>0.9349</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1508</v>
+        <v>-0.4215</v>
       </c>
       <c r="V11" t="n">
         <v>-0.678</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.695</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.243</v>
+        <v>-2.3729</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4994999999999998</v>
+        <v>0.5510000000000006</v>
       </c>
       <c r="E12" t="n">
-        <v>2.735400000000001</v>
+        <v>2.7356</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.235799999999999</v>
+        <v>-2.1846</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6379</v>
@@ -1363,22 +1363,22 @@
         <v>-5.8606</v>
       </c>
       <c r="J12" t="n">
-        <v>4.324599999999998</v>
+        <v>4.3246</v>
       </c>
       <c r="K12" t="n">
-        <v>5.416</v>
+        <v>5.415999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>-1.0916</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.9623</v>
+        <v>-6.962300000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-2.1929</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.769200000000001</v>
+        <v>-4.7692</v>
       </c>
       <c r="P12" t="n">
         <v>4.350099999999999</v>
@@ -1390,13 +1390,13 @@
         <v>15.2254</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.0825</v>
+        <v>-3.031099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7089000000000001</v>
+        <v>-0.709</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3736</v>
+        <v>-2.3221</v>
       </c>
       <c r="V12" t="n">
         <v>1.8695</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2217</v>
+        <v>4.3064</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8418</v>
+        <v>3.6183</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3799</v>
+        <v>0.6881</v>
       </c>
       <c r="G13" t="n">
         <v>4.5952</v>
@@ -1468,13 +1468,13 @@
         <v>2.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>0.149</v>
+        <v>0.2337</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7487</v>
+        <v>0.5252</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5997</v>
+        <v>-0.2914</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. IGLESIAS FERNANDEZ</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2299</v>
+        <v>1.4042</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6925</v>
+        <v>1.0579</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4626</v>
+        <v>0.3463</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0683</v>
+        <v>0.8351</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0037</v>
+        <v>0.581</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0645</v>
+        <v>0.2542</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5361</v>
+        <v>0.9293</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5361</v>
+        <v>0.6998</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.2295</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4679</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5324</v>
+        <v>-0.1188</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0645</v>
+        <v>0.0247</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0964</v>
+        <v>0.7192</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9612</v>
+        <v>0.1286</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1352</v>
+        <v>0.5906</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9347</v>
+        <v>-1.8902</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>M. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8357</v>
+        <v>0.7347</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0579</v>
+        <v>2.3514</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7778</v>
+        <v>-1.6168</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8351</v>
+        <v>1.0683</v>
       </c>
       <c r="H15" t="n">
-        <v>0.581</v>
+        <v>1.0037</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2542</v>
+        <v>0.0645</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9293</v>
+        <v>1.5361</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6998</v>
+        <v>1.5361</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2295</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.4679</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1188</v>
+        <v>-0.5324</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0247</v>
+        <v>0.0645</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1507</v>
+        <v>0.6011</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1286</v>
+        <v>0.6201</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0221</v>
+        <v>-0.0189</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8902</v>
+        <v>-0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8902</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>C. JÜRGENS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5606</v>
+        <v>0.6496</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4443</v>
+        <v>2.4834</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8837</v>
+        <v>-1.8339</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3237</v>
+        <v>0.1338</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8879</v>
+        <v>0.1155</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5642</v>
+        <v>0.0183</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5004</v>
+        <v>0.9507</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1881</v>
+        <v>0.9125</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6885</v>
+        <v>0.0382</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8169</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6998</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1243</v>
+        <v>-0.0199</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>1.949</v>
+        <v>-0.2668</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8362</v>
+        <v>-0.1622</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1128</v>
+        <v>-0.1046</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4997</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>1.695</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. JÜRGENS</t>
+          <t>A. VRABAC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.4534</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3717</v>
+        <v>-0.4566</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8339</v>
+        <v>0.91</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1338</v>
+        <v>-0.6363</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1155</v>
+        <v>-0.7574</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0183</v>
+        <v>0.1211</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9507</v>
+        <v>-0.4281</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9125</v>
+        <v>0.2404</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0382</v>
+        <v>-0.6686</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8169</v>
+        <v>-0.2082</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.9978</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0199</v>
+        <v>0.7897</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3785</v>
+        <v>-0.4753</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.274</v>
+        <v>-0.0709</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1046</v>
+        <v>-0.4044</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.695</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2167</v>
+        <v>0.4209</v>
       </c>
       <c r="E18" t="n">
-        <v>0.073</v>
+        <v>0.1848</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1437</v>
+        <v>0.2362</v>
       </c>
       <c r="G18" t="n">
         <v>0.155</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0616</v>
+        <v>0.2659</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1118</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. VRABAC</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2788</v>
+        <v>-0.1408</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1271</v>
+        <v>0.7738</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8484</v>
+        <v>-0.9146</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6363</v>
+        <v>-0.3237</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7574</v>
+        <v>-0.8879</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1211</v>
+        <v>0.5642</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4281</v>
+        <v>0.5004</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2404</v>
+        <v>-0.1881</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6686</v>
+        <v>0.6885</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2082</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9978</v>
+        <v>-0.6998</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7897</v>
+        <v>-0.1243</v>
       </c>
       <c r="P19" t="n">
         <v>0.435</v>
@@ -1936,22 +1936,22 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2075</v>
+        <v>1.2477</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7413999999999999</v>
+        <v>1.1657</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.466</v>
+        <v>0.082</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>-1.4997</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7483</v>
+        <v>-1.3707</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5361</v>
+        <v>-1.3126</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2121</v>
+        <v>-0.058</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7565</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4693</v>
+        <v>-0.0916</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.125</v>
+        <v>0.0985</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V20" t="n">
         <v>1.13</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARBALLO</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9507</v>
+        <v>-1.4143</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1663</v>
+        <v>-1.7434</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2156</v>
+        <v>0.329</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2808</v>
+        <v>0.7385</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5541</v>
+        <v>-1.5206</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7267</v>
+        <v>2.2591</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.993</v>
+        <v>1.3292</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2862</v>
+        <v>-0.3737</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7068</v>
+        <v>1.7029</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2878</v>
+        <v>-0.5907</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2679</v>
+        <v>-1.1468</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0199</v>
+        <v>0.5562</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>-2.1751</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3426</v>
+        <v>0.0222</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.411</v>
+        <v>-0.3749</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0684</v>
+        <v>0.3972</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3252</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. SARAIVA SEIXAS</t>
+          <t>M. FERNANDEZ CARBALLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.012</v>
+        <v>-1.6463</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8847</v>
+        <v>-1.831</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1273</v>
+        <v>0.1848</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4661</v>
+        <v>-2.2808</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0365</v>
+        <v>-1.5541</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4296</v>
+        <v>-0.7267</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6519</v>
+        <v>-1.993</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2039</v>
+        <v>-1.2862</v>
       </c>
       <c r="L22" t="n">
-        <v>2.448</v>
+        <v>-0.7068</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1858</v>
+        <v>-0.2878</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1674</v>
+        <v>-0.2679</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0184</v>
+        <v>-0.0199</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.6101</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>0.262</v>
+        <v>-0.0382</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.274</v>
+        <v>-0.0757</v>
       </c>
       <c r="U22" t="n">
-        <v>0.536</v>
+        <v>0.0375</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>D. SARAIVA SEIXAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0463</v>
+        <v>-1.7885</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1904</v>
+        <v>-0.6612</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1441</v>
+        <v>-1.1273</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7385</v>
+        <v>1.4661</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5206</v>
+        <v>0.0365</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2591</v>
+        <v>1.4296</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3292</v>
+        <v>2.6519</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3737</v>
+        <v>0.2039</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7029</v>
+        <v>2.448</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5907</v>
+        <v>-1.1858</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1468</v>
+        <v>-0.1674</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5562</v>
+        <v>-1.0184</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1751</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q23" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6097</v>
+        <v>0.4855</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.0505</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2122</v>
+        <v>0.536</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0658</v>
+        <v>-2.1081</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3405</v>
+        <v>-2.2288</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2748</v>
+        <v>0.1206</v>
       </c>
       <c r="G24" t="n">
         <v>-1.357</v>
@@ -2326,13 +2326,13 @@
         <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4212</v>
+        <v>0.3788</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3461</v>
+        <v>0.4579</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0751</v>
+        <v>-0.079</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4994999999999989</v>
+        <v>-0.4995000000000007</v>
       </c>
       <c r="E25" t="n">
-        <v>2.236100000000001</v>
+        <v>2.235999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.735300000000001</v>
+        <v>-2.7356</v>
       </c>
       <c r="G25" t="n">
         <v>2.6377</v>
@@ -2377,13 +2377,13 @@
         <v>5.860899999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>6.962400000000001</v>
+        <v>6.962399999999999</v>
       </c>
       <c r="K25" t="n">
         <v>2.1929</v>
       </c>
       <c r="L25" t="n">
-        <v>4.769200000000001</v>
+        <v>4.769199999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-4.3247</v>
@@ -2404,13 +2404,13 @@
         <v>10.8752</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0823</v>
+        <v>3.082200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3734</v>
+        <v>2.3736</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7087999999999999</v>
+        <v>0.7089000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8694</v>
@@ -2419,7 +2419,7 @@
         <v>8.1258</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.9954</v>
+        <v>-9.995400000000002</v>
       </c>
     </row>
   </sheetData>
